--- a/pipelines/Demo_data/Output_data/out_Монитор.xlsx
+++ b/pipelines/Demo_data/Output_data/out_Монитор.xlsx
@@ -494,10 +494,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F2" t="n">
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -546,10 +544,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F3" t="n">
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -598,10 +594,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F4" t="n">
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -650,10 +644,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F5" t="n">
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -702,10 +694,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -754,10 +744,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F7" t="n">
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -806,10 +794,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F8" t="n">
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -858,10 +844,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -910,10 +894,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -962,10 +944,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1014,10 +994,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F12" t="n">
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1066,10 +1044,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1118,10 +1094,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1170,10 +1144,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F15" t="n">
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1214,10 +1186,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>15195.02</t>
-        </is>
+      <c r="F16" t="n">
+        <v>15195.02</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1258,10 +1228,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1302,10 +1270,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F18" t="n">
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1346,10 +1312,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F19" t="n">
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1390,10 +1354,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F20" t="n">
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1434,10 +1396,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F21" t="n">
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1478,10 +1438,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F22" t="n">
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1522,10 +1480,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F23" t="n">
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1566,10 +1522,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F24" t="n">
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1610,10 +1564,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F25" t="n">
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1654,10 +1606,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F26" t="n">
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1698,10 +1648,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>65369.98</t>
-        </is>
+      <c r="F27" t="n">
+        <v>65369.98</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1742,10 +1690,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F28" t="n">
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1794,10 +1740,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F29" t="n">
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1846,10 +1790,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F30" t="n">
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1898,10 +1840,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F31" t="n">
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1950,10 +1890,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F32" t="n">
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2002,10 +1940,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F33" t="n">
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2054,10 +1990,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F34" t="n">
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2106,10 +2040,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F35" t="n">
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>

--- a/pipelines/Demo_data/Output_data/out_Монитор.xlsx
+++ b/pipelines/Demo_data/Output_data/out_Монитор.xlsx
@@ -494,8 +494,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,8 +546,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -594,8 +598,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,8 +650,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -694,8 +702,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -744,8 +754,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -794,8 +806,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -844,8 +858,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -894,8 +910,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -944,8 +962,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -994,8 +1014,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1044,8 +1066,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1094,8 +1118,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1144,8 +1170,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1186,8 +1214,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>15195.02</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>15195.02</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1228,8 +1258,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1270,8 +1302,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1312,8 +1346,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1354,8 +1390,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1396,8 +1434,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1438,8 +1478,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1480,8 +1522,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1522,8 +1566,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1564,8 +1610,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1606,8 +1654,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1648,8 +1698,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>65369.98</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>65369.98</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1690,8 +1742,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1740,8 +1794,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1790,8 +1846,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1840,8 +1898,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1890,8 +1950,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1940,8 +2002,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1990,8 +2054,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>0</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2040,8 +2106,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>0</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
